--- a/Zeiterfassung.xlsx
+++ b/Zeiterfassung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\awrDATEN\lena\DATA SCIENCE INSTITUTE\Projekt_Zeiterfassung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98EE1558-E02A-4674-8982-4D21DC3CBBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A6F757-F303-4C01-BC64-D6E245C33C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maerz" sheetId="1" r:id="rId1"/>
